--- a/data/externalStats/File2/TC9_Exc_External.xlsx
+++ b/data/externalStats/File2/TC9_Exc_External.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ms.ds.uhc.com\userdata\030\amitta73\Desktop\RAO_Automation\data\externalStats\File2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ms.ds.uhc.com\userdata\030\amitta73\Desktop\RPT_Automation\data\externalStats\File2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{69DF72EB-CEB7-4FE8-9F28-F6F0EBCBA1BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{27217D55-50BD-4336-8A73-1123EFB76632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{63FFEFF0-31F1-43F3-92F9-0B3BF547B0E7}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{9AAF969D-C553-4233-BE98-49E9A7403351}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -793,7 +793,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F16DE154-183A-40AC-BF15-BE0D8A9726FD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C51743C-852D-4D46-88A8-ACA144069A50}">
   <dimension ref="A15:AN153"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
